--- a/排课结果/调课时调整的已排课程.xlsx
+++ b/排课结果/调课时调整的已排课程.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,199 +501,173 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>150000290.029</t>
+          <t>15ALT049.001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>软件学院</t>
-        </is>
-      </c>
+          <t>足球甲组业余集训</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>新新龙</t>
+          <t>新刚</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>xkp01230083</t>
+          <t>xkp01230325</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>北校区篮球3</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>305</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CLS1514</t>
+          <t>CLS1003</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>大数据2401 大数据2402 大数据2403 大数据2404 大数据2405 大数据2406 大数据2407 大数据2408</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>周五（5-6节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>150000290.029</t>
+          <t>61421014.001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>软件学院</t>
-        </is>
-      </c>
+          <t>当代英语小说选读</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>新新龙</t>
+          <t>新小静</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>xkp01230083</t>
+          <t>xkp01230398</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>41</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>北校区篮球4</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H3" t="n">
+        <v>305</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CLS1515</t>
+          <t>CLS1003</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>大数据2401 大数据2402 大数据2403 大数据2404 大数据2405 大数据2406 大数据2407 大数据2408</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>周五（5-6节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>150000290.025</t>
+          <t>61421016.001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>工商管理学院</t>
-        </is>
-      </c>
+          <t>英语话中国传统节日</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>新晨阳</t>
+          <t>新玉体</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>xkp01231126</t>
+          <t>xkp01020044</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>乒乓球训练房2</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H4" t="n">
+        <v>305</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CLS1316</t>
+          <t>CLS1003</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -703,75 +677,65 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>工商类2401 工商类2402 工商类2403 工商类2404 工商类2405 工商类2406 工商类2407 工商类2408 工商类2409 工商类2410 工商类2411 工商类2412 工业2401 工业2402 工业2403 旅游2401 旅游2402</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>周五（5-6节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>150000290.049</t>
+          <t>61421014.001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>机械与动力工程学院</t>
-        </is>
-      </c>
+          <t>当代英语小说选读</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新娜娜</t>
+          <t>新小静</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>xkp01230661</t>
+          <t>xkp01230398</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>42</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>武术训练房1</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H5" t="n">
+        <v>305</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CLS1317</t>
+          <t>CLS1003</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -781,75 +745,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>机械学院，周五5.6</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>周一（3-4节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周四</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>150000290.017</t>
+          <t>61421014.001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>电气工程与自动化学院</t>
-        </is>
-      </c>
+          <t>当代英语小说选读</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>新娜娜</t>
+          <t>新小静</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>xkp01230661</t>
+          <t>xkp01230398</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>43</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>乒乓球训练房1</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H6" t="n">
+        <v>305</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CLS1315</t>
+          <t>CLS1003</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -859,75 +813,65 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>电气学院，周一3.41</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>周四（5-6节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>150000290.104</t>
+          <t>61421016.001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>工商管理学院</t>
-        </is>
-      </c>
+          <t>英语话中国传统节日</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>新清华</t>
+          <t>新玉体</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>xkp01050044</t>
+          <t>xkp01020044</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>舞操训练房1</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H7" t="n">
+        <v>304</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CLS1319</t>
+          <t>CLS1004</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -937,75 +881,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>工商类2401 工商类2402 工商类2403 工商类2404 工商类2405 工商类2406 工商类2407 工商类2408 工商类2409 工商类2410 工商类2411 工商类2412 工业2401 工业2402 工业2403 旅游2401 旅游2402</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>周三（3-4节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>150000290.105</t>
+          <t>61421014.001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>工商管理学院</t>
-        </is>
-      </c>
+          <t>当代英语小说选读</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>新俊魁</t>
+          <t>新小静</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>xkp01050057</t>
+          <t>xkp01230398</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>45</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>乒乓球训练房3</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H8" t="n">
+        <v>304</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CLS1331</t>
+          <t>CLS1004</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1015,100 +949,86 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>工商类2401 工商类2402 工商类2403 工商类2404 工商类2405 工商类2406 工商类2407 工商类2408 工商类2409 工商类2410 工商类2411 工商类2412 工业2401 工业2402 工业2403 旅游2401 旅游2402</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>周三（3-4节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>150000290.131</t>
+          <t>61421014.001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>软件学院</t>
-        </is>
-      </c>
+          <t>当代英语小说选读</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>新洁</t>
+          <t>新小静</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>xkp01050028</t>
+          <t>xkp01230398</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>乒乓球训练房</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H9" t="n">
+        <v>304</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CLS1511</t>
+          <t>CLS1004</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>软件2401 软件2402 软件2403 软件2404 软件2405 软件2406 软件2407 软件2408 软件2409</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>周三（5-6节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1118,128 +1038,112 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>150000290.137</t>
+          <t>61421016.001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>软件学院</t>
-        </is>
-      </c>
+          <t>英语话中国传统节日</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>新刚</t>
+          <t>新玉体</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>xkp01230325</t>
+          <t>xkp01020044</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>健身房</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H10" t="n">
+        <v>304</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CLS1509</t>
+          <t>CLS1004</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>网安2401 网安2402 网安2403 网安2404 网安2405 网安2406 网安2407 网安2408</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>周二（3-4节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>150000290.024</t>
+          <t>61421014.001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>计算机科学与技术学院 能源科学与工程学院</t>
-        </is>
-      </c>
+          <t>当代英语小说选读</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>新娜娜</t>
+          <t>新小静</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>xkp01230661</t>
+          <t>xkp01230398</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>44</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>舞操训练房2</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H11" t="n">
+        <v>304</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CLS1320</t>
+          <t>CLS1004</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1249,22 +1153,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>计算机2401 计算机2402 计算机2403 计算机2404 计算机2405 计实验2401 物联网2401 物联网2402 物联网2403 智采2401 智采2402 智采2403 采矿卓2401 采矿卓2402 新能科2401 新能科2402 交通2401 交通2402 交通2403 机器感知与机器视觉2401 机器感知与机器视觉2402</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>周五（5-6节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1281,43 +1181,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>150000290.014</t>
+          <t>61421014.001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>测绘与国土信息工程学院</t>
-        </is>
-      </c>
+          <t>当代英语小说选读</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>新枫</t>
+          <t>新小静</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>xkp01050026</t>
+          <t>xkp01230398</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>48</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>东区足球1</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H12" t="n">
+        <v>301</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CLS1332</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1327,75 +1221,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>测绘卓2401 测绘卓2402 测绘卓2403 测绘卓2404 测绘2401 测绘2402 测绘2403 测绘2404 遥感2401 遥感2402 遥感2403 遥感2404 土管2401 土管2402 地信2401 地信2402 地信2403 自环2401 城乡2401 城乡2402</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>周三（3-4节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>150000290.018</t>
+          <t>61421016.001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>化学化工学院 资源环境学院 资源环境学院</t>
-        </is>
-      </c>
+          <t>英语话中国传统节日</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>新俊魁</t>
+          <t>新玉体</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>xkp01050057</t>
+          <t>xkp01020044</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>46</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>乒乓球训练房1</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H13" t="n">
+        <v>301</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CLS1315</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1405,75 +1289,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>矿加2401 矿加卓2401 矿加卓2402 应化2401 应化2402 应化2403 化工2401 化工2402 化工2403 化工2404 储能2401 储能2402 储能2403 地质2401 地质2402 地质卓2401 地科2401 地科2402 地科2403 水文2401 水文2402 水文2403 勘查拔尖班2401 勘查清洁2401 勘查清洁2402 勘查战略2401 勘查战略2402 环境2401 环境2402 环境生态2401 环境生态2402</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>周五（3-4节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>150000290.020</t>
+          <t>61421016.001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>财经学院 音乐学院 应急管理学院</t>
-        </is>
-      </c>
+          <t>英语话中国传统节日</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>新澳伟</t>
+          <t>新玉体</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>xkp01231162</t>
+          <t>xkp01020044</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>44</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>乒乓球训练房2</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="H14" t="n">
+        <v>301</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CLS1316</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1483,75 +1357,65 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>会计2401 会计2402 会计2403 会计2404 会计2405 财管2401 财管2402 财管2403 财管2404 数字经济2401 数字经济2402 数字经济2403 金融2401 金融2402 金融2403 音乐2401 音乐2402 音乐2403 管理2401 管理2402 应急2401 应急2402 音乐2404 应急2403</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>周三（5-6节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>150000290.011</t>
+          <t>15ALT049.001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>物理与电子信息学院</t>
-        </is>
-      </c>
+          <t>足球甲组业余集训</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>新晨阳</t>
+          <t>新刚</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>xkp01231126</t>
+          <t>xkp01230325</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>武术训练房2</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>301</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CLS1318</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1561,75 +1425,65 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>电信2401 电信2402 人工智能2401 人工智能2402 人工智能2403 微电子2401 微电子2402 微电子2403 通信2401 通信2402 通信2403 通信2404 电信合2401 电信合2402 电信合2403 电信合2404 物理2401 物理2402</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>周四（3-4节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>150000290.046</t>
+          <t>15ALT049.001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>机械与动力工程学院</t>
-        </is>
-      </c>
+          <t>足球甲组业余集训</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>新红卫</t>
+          <t>新刚</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>xkp01050070</t>
+          <t>xkp01230325</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>42</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>乒乓球训练房3</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>301</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CLS1331</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1639,27 +1493,23 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>机械学院，周五5.6</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>周一（3-4节）</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1671,43 +1521,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>150000290.052</t>
+          <t>120000251.052</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>形势与政策-3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>机械与动力工程学院</t>
+          <t>资源环境学院</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>新澳伟</t>
+          <t>新德新</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>xkp01231162</t>
+          <t>xkp01120069</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>41</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>东区足球2</t>
-        </is>
+        <v>83</v>
+      </c>
+      <c r="H17" t="n">
+        <v>301</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CLS1333</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1717,22 +1565,18 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>机械学院，周五5.6</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>周一（3-4节）</t>
-        </is>
-      </c>
+          <t>地科2401 地科2402 地科2403</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1742,231 +1586,213 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第11-11节</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>150000290.188</t>
+          <t>120000251.052</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>形势与政策-3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>建筑与艺术设计学院</t>
+          <t>资源环境学院</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>新燕桐</t>
+          <t>新德新</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>xkp01170064</t>
+          <t>xkp01120069</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>42</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>北校区篮球1</t>
-        </is>
+        <v>83</v>
+      </c>
+      <c r="H18" t="n">
+        <v>301</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CLS1512</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>建筑类2401 建筑类2402 建筑类2403 建筑类2404 设计类2401 设计类2402 设计类2403 设计类2404 设计类2405 设计类2406 工设2401 工设2402 建筑类2405</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>周五（3-4节）</t>
-        </is>
-      </c>
+          <t>地科2401 地科2402 地科2403</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>150000290.155</t>
+          <t>120000310.012</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>毛泽东思想和中国特色社会主义理论体系概论</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>医学院</t>
+          <t>工商管理学院</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>新燕桐</t>
+          <t>新新新</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>xkp01170064</t>
+          <t>xkp01010187</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>42</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>舞操训练房</t>
-        </is>
+        <v>107</v>
+      </c>
+      <c r="H19" t="n">
+        <v>301</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CLS1510</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>护理2401 护理2402 药学2401 药学2402 药学2403 药学2404 临床医学2401 临床医学2402 临床医学2403</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>周四（3-4节）</t>
-        </is>
-      </c>
+          <t>工商2301 工商2302 工商2303 工商2304</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>150000290.152</t>
+          <t>120000310.012</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>毛泽东思想和中国特色社会主义理论体系概论</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>医学院</t>
+          <t>工商管理学院</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>新刚</t>
+          <t>新新新</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>xkp01230325</t>
+          <t>xkp01010187</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>42</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>健身房</t>
-        </is>
+        <v>107</v>
+      </c>
+      <c r="H20" t="n">
+        <v>301</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CLS1509</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>护理2401 护理2402 药学2401 药学2402 药学2403 药学2404 临床医学2401 临床医学2402 临床医学2403</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>周四（3-4节）</t>
-        </is>
-      </c>
+          <t>工商2301 工商2302 工商2303 工商2304</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1976,122 +1802,120 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>150000290.153</t>
+          <t>11200009.019</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>线性代数b</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>医学院</t>
+          <t>机械与动力工程学院</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>新永胜</t>
+          <t>新艳丽</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>xkp01050040</t>
+          <t>xkp01040037</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>42</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>健身房</t>
-        </is>
+        <v>155</v>
+      </c>
+      <c r="H21" t="n">
+        <v>301</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CLS1509</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>护理2401 护理2402 药学2401 药学2402 药学2403 药学2404 临床医学2401 临床医学2402 临床医学2403</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>周四（3-4节）</t>
-        </is>
-      </c>
+          <t>机械2501 机械2502 机械2503 机械2504 机械2505</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>1,2,3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>15ALT049.001</t>
+          <t>11200009.019</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>足球甲组业余集训</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>线性代数b</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>新刚</t>
+          <t>新艳丽</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>xkp01230325</t>
+          <t>xkp01040037</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="H22" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CLS1003</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2101,7 +1925,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>机械2501 机械2502 机械2503 机械2504 机械2505</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2112,47 +1936,51 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
+          <t>1,2,3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15ALT049.001</t>
+          <t>04404003.001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>足球甲组业余集训</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>智能制造工程专业导论</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>新刚</t>
+          <t>新俊杰</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>xkp01230325</t>
+          <t>xkp01080057</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H23" t="n">
         <v>305</v>
@@ -2169,7 +1997,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -2180,7 +2008,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2190,37 +2018,41 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>61421014.001</t>
+          <t>04404003.001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>当代英语小说选读</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>智能制造工程专业导论</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>新小静</t>
+          <t>新绍亮</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>xkp01230398</t>
+          <t>xkp01080152</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H24" t="n">
         <v>305</v>
@@ -2237,7 +2069,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -2248,12 +2080,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2265,30 +2097,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>61421016.001</t>
+          <t>04404003.001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>英语话中国传统节日</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>智能制造工程专业导论</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>新玉体</t>
+          <t>新俊杰</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>xkp01020044</t>
+          <t>xkp01080057</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H25" t="n">
         <v>305</v>
@@ -2305,7 +2141,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2316,47 +2152,51 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>61421016.001</t>
+          <t>04404003.001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>英语话中国传统节日</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>智能制造工程专业导论</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>新玉体</t>
+          <t>新绍亮</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>xkp01020044</t>
+          <t>xkp01080152</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H26" t="n">
         <v>305</v>
@@ -2373,7 +2213,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2384,7 +2224,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2394,37 +2234,41 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>61421016.001</t>
+          <t>040961500.002</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>英语话中国传统节日</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>信号分析与处理（双语）</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>新玉体</t>
+          <t>新春朝</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>xkp01020044</t>
+          <t>xkp01080077</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H27" t="n">
         <v>304</v>
@@ -2441,7 +2285,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>测控2403 测控2404</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2452,7 +2296,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2462,37 +2306,41 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>61421014.001</t>
+          <t>040961500.002</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>当代英语小说选读</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>信号分析与处理（双语）</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>新小静</t>
+          <t>新春朝</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>xkp01230398</t>
+          <t>xkp01080077</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H28" t="n">
         <v>304</v>
@@ -2509,7 +2357,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>测控2403 测控2404</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2520,54 +2368,58 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周四</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>61421014.001</t>
+          <t>12100001.036</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>当代英语小说选读</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>思想道德与法治</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>财经学院</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>新小静</t>
+          <t>新一新</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>xkp01230398</t>
+          <t>xkp01010198</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H29" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2577,7 +2429,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>金融2501 金融2502 金融2503</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2588,7 +2440,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2598,44 +2450,48 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>61421014.001</t>
+          <t>12100001.036</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>当代英语小说选读</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>思想道德与法治</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>财经学院</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>新小静</t>
+          <t>新一新</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>xkp01230398</t>
+          <t>xkp01010198</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H30" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2645,7 +2501,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>金融2501 金融2502 金融2503</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2656,7 +2512,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2666,44 +2522,48 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>61421014.001</t>
+          <t>13200002.016</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>当代英语小说选读</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>能源科学与工程学院</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>新小静</t>
+          <t>新岩松</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>xkp01230398</t>
+          <t>xkp01030050</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H31" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2713,7 +2573,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>新能科2501 新能科2502 新能科2503</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2724,47 +2584,51 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>周四</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>61421014.001</t>
+          <t>13200002.016</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>当代英语小说选读</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>能源科学与工程学院</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>新小静</t>
+          <t>新岩松</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>xkp01230398</t>
+          <t>xkp01030050</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H32" t="n">
         <v>301</v>
@@ -2781,7 +2645,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>新能科2501 新能科2502 新能科2503</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2792,12 +2656,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2809,30 +2673,34 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>61421016.001</t>
+          <t>090000112.003</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>英语话中国传统节日</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>计算机组成原理</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>计算机科学与技术学院</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>新玉体</t>
+          <t>新静</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>xkp01020044</t>
+          <t>xkp01070073</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="H33" t="n">
         <v>301</v>
@@ -2849,7 +2717,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>计算机2401 计算机2402</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2860,12 +2728,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2877,30 +2745,34 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>61421014.001</t>
+          <t>090000112.003</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>当代英语小说选读</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>计算机组成原理</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>计算机科学与技术学院</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>新小静</t>
+          <t>新静</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>xkp01230398</t>
+          <t>xkp01070073</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="H34" t="n">
         <v>301</v>
@@ -2917,7 +2789,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>计算机2401 计算机2402</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2928,47 +2800,51 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>61421014.001</t>
+          <t>07406007.001</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>当代英语小说选读</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>管理学原理</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>土木工程学院</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>新小静</t>
+          <t>新瑚均</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>xkp01230398</t>
+          <t>xkp01230621</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="H35" t="n">
         <v>301</v>
@@ -2985,7 +2861,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>工管2501 工管2502</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2996,47 +2872,51 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周四</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>61421016.001</t>
+          <t>07406007.001</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>英语话中国传统节日</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>管理学原理</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>土木工程学院</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>新玉体</t>
+          <t>新瑚均</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>xkp01020044</t>
+          <t>xkp01230621</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="H36" t="n">
         <v>301</v>
@@ -3053,7 +2933,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>工管2501 工管2502</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -3064,12 +2944,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3081,37 +2961,41 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>61421014.001</t>
+          <t>09200007.014</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>当代英语小说选读</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>C语言程序设计b</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>新小静</t>
+          <t>新勇刚</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>xkp01230398</t>
+          <t>xkp01080078</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="H37" t="n">
-        <v>301</v>
+        <v>2103</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3121,7 +3005,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>测控2503 测控2504</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -3132,12 +3016,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3149,37 +3033,41 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>61421016.001</t>
+          <t>09200007.014</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>英语话中国传统节日</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>C语言程序设计b</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>新玉体</t>
+          <t>新勇刚</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>xkp01020044</t>
+          <t>xkp01080078</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="H38" t="n">
-        <v>301</v>
+        <v>2103</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3189,7 +3077,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>测控2503 测控2504</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -3200,7 +3088,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3210,44 +3098,48 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>61421016.001</t>
+          <t>080080010.001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>英语话中国传统节日</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>电工与电子技术-2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>新玉体</t>
+          <t>新涛</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>xkp01020044</t>
+          <t>xkp01060128</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H39" t="n">
-        <v>301</v>
+        <v>2103</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3257,7 +3149,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>车辆2401 车辆2402</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -3268,54 +3160,58 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>3,4,5,6,7,8,9,10</t>
+          <t>1,2,3,4,5,6,7</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>15ALT049.001</t>
+          <t>080080010.001</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>足球甲组业余集训</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>电工与电子技术-2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>新刚</t>
+          <t>新涛</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>xkp01230325</t>
+          <t>xkp01060128</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H40" t="n">
-        <v>301</v>
+        <v>2103</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3325,7 +3221,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>车辆2401 车辆2402</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -3336,7 +3232,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
+          <t>1,2,3,4,5,6,7</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3353,37 +3249,41 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>61421014.001</t>
+          <t>041953005.001</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>当代英语小说选读</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>太阳能热利用原理与技术</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>能源科学与工程学院</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>新小静</t>
+          <t>新新新</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>xkp01230398</t>
+          <t>xkp01230794</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="H41" t="n">
-        <v>301</v>
+        <v>2103</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3393,7 +3293,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>新能科2301 新能科2302</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -3409,7 +3309,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3421,37 +3321,41 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15ALT049.001</t>
+          <t>041953005.001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>足球甲组业余集训</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>太阳能热利用原理与技术</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>能源科学与工程学院</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>新刚</t>
+          <t>新新新</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>xkp01230325</t>
+          <t>xkp01230794</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H42" t="n">
-        <v>301</v>
+        <v>2103</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3461,7 +3365,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>新能科2301 新能科2302</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3472,54 +3376,58 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
+          <t>3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>15ALT049.001</t>
+          <t>09200005.006</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>足球甲组业余集训</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Python语言程序设计b</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>新刚</t>
+          <t>新本仓</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>xkp01230325</t>
+          <t>xkp01200138</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H43" t="n">
-        <v>301</v>
+        <v>2103</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3529,7 +3437,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>材科2501 材科2502</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -3540,12 +3448,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3557,37 +3465,41 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15ALT049.001</t>
+          <t>09200005.006</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>足球甲组业余集训</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Python语言程序设计b</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>新刚</t>
+          <t>新本仓</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>xkp01230325</t>
+          <t>xkp01200138</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H44" t="n">
-        <v>301</v>
+        <v>2103</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3597,7 +3509,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>材科2501 材科2502</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3608,7 +3520,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3618,44 +3530,48 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15ALT049.001</t>
+          <t>040930700.001</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>足球甲组业余集训</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>传感器与检测技术</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>新刚</t>
+          <t>新业新</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>xkp01230325</t>
+          <t>xkp01080136</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H45" t="n">
-        <v>301</v>
+        <v>2103</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3665,7 +3581,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>全校</t>
+          <t>智能制造2301 智能制造2302</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3676,60 +3592,58 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
+          <t>1,2,3,4,5,6,7</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>第7-8节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>150000290.058</t>
+          <t>040930700.001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>传感器与检测技术</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>电气工程与自动化学院</t>
+          <t>机械与动力工程学院</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>新孝志</t>
+          <t>新业新</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>xkp01050019</t>
+          <t>xkp01080136</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>45</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>东区排球2</t>
-        </is>
+        <v>65</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2103</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CLS1335</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3739,27 +3653,23 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>电气学院，周一3.47</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>周一（3-4节）</t>
-        </is>
-      </c>
+          <t>智能制造2301 智能制造2302</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>1,2,3,4,5,6,7</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周四</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -3771,43 +3681,41 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>150000290.058</t>
+          <t>020060140.001</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>新能源勘查方法与技术</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>电气工程与自动化学院</t>
+          <t>能源科学与工程学院</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>新娟</t>
+          <t>新小凯</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>xkp01050085</t>
+          <t>xkp01230493</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>45</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>东区排球2</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2103</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CLS1335</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3817,75 +3725,69 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>电气学院，周一3.47</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>周一（3-4节）</t>
-        </is>
-      </c>
+          <t>新能科2401 新能科2402</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>150000290.049</t>
+          <t>020060140.001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>新能源勘查方法与技术</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>机械与动力工程学院</t>
+          <t>能源科学与工程学院</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>新娜娜</t>
+          <t>新硕</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>xkp01230661</t>
+          <t>xkp01230584</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G48" t="n">
-        <v>42</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>武术训练房1</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2103</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CLS1317</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3895,75 +3797,69 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>机械学院，周五5.6</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>周一（3-4节）</t>
-        </is>
-      </c>
+          <t>新能科2401 新能科2402</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>150000290.045</t>
+          <t>020060140.001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>新能源勘查方法与技术</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>机械与动力工程学院</t>
+          <t>能源科学与工程学院</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>新建平</t>
+          <t>新小凯</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>xkp01050048</t>
+          <t>xkp01230493</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
-        <v>42</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>健身实训中心</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2103</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CLS1321</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3973,75 +3869,69 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>机械学院，周五5.6</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>周一（3-4节）</t>
-        </is>
-      </c>
+          <t>新能科2401 新能科2402</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周四</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>150000290.168</t>
+          <t>020060140.001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>新能源勘查方法与技术</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>化学化工学院 资源环境学院 资源环境学院</t>
+          <t>能源科学与工程学院</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>新建平</t>
+          <t>新硕</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>xkp01050048</t>
+          <t>xkp01230584</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>45</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>乒乓球训练房2</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2103</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CLS1316</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4051,22 +3941,18 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>矿加2401 矿加卓2401 矿加卓2402 应化2401 应化2402 应化2403 化工2401 化工2402 化工2403 化工2404 储能2401 储能2402 储能2403 地质2401 地质2402 地质卓2401 地科2401 地科2402 地科2403 水文2401 水文2402 水文2403 勘查拔尖班2401 勘查清洁2401 勘查清洁2402 勘查战略2401 勘查战略2402 环境2401 环境2402 环境生态2401 环境生态2402</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>周四（5-6节）</t>
-        </is>
-      </c>
+          <t>新能科2401 新能科2402</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4083,43 +3969,41 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>150000290.150</t>
+          <t>12100008.039</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>形势与政策-1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>测绘与国土信息工程学院</t>
+          <t>机械与动力工程学院</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>新建平</t>
+          <t>新彦</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>xkp01050048</t>
+          <t>xkp01200063</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51" t="n">
-        <v>45</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>舞操训练房1</t>
-        </is>
+        <v>94</v>
+      </c>
+      <c r="H51" t="n">
+        <v>305</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CLS1319</t>
+          <t>CLS1003</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4129,75 +4013,69 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>测绘卓2401 测绘卓2402 测绘卓2403 测绘卓2404 测绘2401 测绘2402 测绘2403 测绘2404 遥感2401 遥感2402 遥感2403 遥感2404 土管2401 土管2402 地信2401 地信2402 地信2403 自环2401 城乡2401 城乡2402</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>周四（3-4节）</t>
-        </is>
-      </c>
+          <t>智能制造2501 智能制造2502 智能制造2503</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>150000290.186</t>
+          <t>12100008.039</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>体育与健康4</t>
+          <t>形势与政策-1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>数学与信息科学学院 安全科学与工程学院</t>
+          <t>机械与动力工程学院</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>新建平</t>
+          <t>新彦</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>xkp01050048</t>
+          <t>xkp01200063</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>43</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>乒乓球训练房2</t>
-        </is>
+        <v>94</v>
+      </c>
+      <c r="H52" t="n">
+        <v>305</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CLS1316</t>
+          <t>CLS1003</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4207,69 +4085,69 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>安全卓2401 安全卓2402 安全卓2403 安全卓2404 安全卓2405 安全卓2406 安全卓2407 安全卓2408 安全卓2409 消防2401 消防2402 数学类2401 数学类2402 数学类2403 数学类2404 数学类2405 数学类2406 数学类2407</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>周五（3-4节）</t>
-        </is>
-      </c>
+          <t>智能制造2501 智能制造2502 智能制造2503</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>周二(5-8节）;全周（1-2节）</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第11-11节</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>15ALT016.001</t>
+          <t>030040030.001</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>队田径业余队</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>环境化学</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>资源环境学院</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>新建平</t>
+          <t>新发扬</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>xkp01050048</t>
+          <t>xkp01230749</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H53" t="n">
-        <v>2103</v>
+        <v>304</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CLS1006</t>
+          <t>CLS1004</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4277,7 +4155,11 @@
           <t>南校区</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>环境2401 环境2402</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
@@ -4286,7 +4168,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+          <t>9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4296,44 +4178,48 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>15ALT016.001</t>
+          <t>030040030.001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>队田径业余队</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>环境化学</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>资源环境学院</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>新建平</t>
+          <t>新发扬</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>xkp01050048</t>
+          <t>xkp01230749</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H54" t="n">
-        <v>2103</v>
+        <v>304</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CLS1006</t>
+          <t>CLS1004</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4341,7 +4227,11 @@
           <t>南校区</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>环境2401 环境2402</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
@@ -4350,47 +4240,51 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+          <t>9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>15ALT016.001</t>
+          <t>11200004.004</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>队田径业余队</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>高等数学b-2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>计算机科学与技术学院</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>新建平</t>
+          <t>新颖芳</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>xkp01050048</t>
+          <t>xkp01040015</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>6</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="H55" t="n">
         <v>2103</v>
@@ -4405,7 +4299,11 @@
           <t>南校区</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>机器感知与机器视觉2501 机器感知与机器视觉2502 计算机2505 计算机2506</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
@@ -4414,7 +4312,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4424,48 +4322,48 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>150010220.001</t>
+          <t>11200004.004</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>体育管理学</t>
+          <t>高等数学b-2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>体育学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>新辉</t>
+          <t>新颖芳</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>xkp01050082</t>
+          <t>xkp01040015</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="H56" t="n">
-        <v>2310</v>
+        <v>2103</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CLS1015</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4475,14 +4373,10 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>体育2401 体育2402</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>周一（3-4节）</t>
-        </is>
-      </c>
+          <t>机器感知与机器视觉2501 机器感知与机器视觉2502 计算机2505 计算机2506</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>周二(5-8节）</t>
@@ -4495,53 +4389,53 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周四</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>151130360.002</t>
+          <t>11200004.004</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>瑜伽</t>
+          <t>高等数学b-2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>体育学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>新辉</t>
+          <t>新颖芳</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>xkp01050082</t>
+          <t>xkp01040015</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G57" t="n">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="H57" t="n">
-        <v>2203</v>
+        <v>2103</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CLS1009</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4551,14 +4445,10 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>体育2402</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>周二（3-4节）</t>
-        </is>
-      </c>
+          <t>机器感知与机器视觉2501 机器感知与机器视觉2502 计算机2505 计算机2506</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>周二(5-8节）</t>
@@ -4571,53 +4461,49 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15502007.001</t>
+          <t>15ALT016.001</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>太极拳文化解析1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>体育学院</t>
-        </is>
-      </c>
+          <t>队田径业余队</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>新辉</t>
+          <t>新建平</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>xkp01050082</t>
+          <t>xkp01050048</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>301</v>
+        <v>2104</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1007</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4625,11 +4511,7 @@
           <t>南校区</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>民传（太极拳实验班）2501</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
@@ -4638,17 +4520,3421 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>15ALT016.001</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>队田径业余队</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>新建平</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>xkp01050048</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>6</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>15ALT016.001</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>队田径业余队</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>新建平</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>xkp01050048</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>6</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>15ALT011.001</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>轮滑冰球队</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>新颜东</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>xkp01050061</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>6</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>15ALT011.001</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>轮滑冰球队</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>新颜东</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>xkp01050061</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>15ALT011.001</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>轮滑冰球队</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>新颜东</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>xkp01050061</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>6</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>14200002.090</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>大学外语2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>财经学院 应急管理学院</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>新莎莎</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>xkp01020019</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>94</v>
+      </c>
+      <c r="H64" t="n">
+        <v>301</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>CLS1005</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>财管2501 财管2502 财管2503 财管2504 会计2501 会计2502 会计2503 会计2504 会计2505 金融2501 金融2502 金融2503 数字经济2501 数字经济2502 数字经济2503 事管2501 事管2502 应急2501 应急25026</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>98200001.006</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>大学生心理健康教育</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>新晓慧</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>xkp01230194</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>85</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2103</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>CLS1006</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>智能材料2501 智能材料2502</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>15502007.001</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>太极拳文化解析1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>体育学院</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>新辉</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>xkp01050082</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>25</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2103</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>CLS1006</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>民传（太极拳实验班）2501</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
           <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>120000251.048</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>形势与政策-3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>工商管理学院</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>新德新</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>xkp01120069</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>3</v>
+      </c>
+      <c r="G67" t="n">
+        <v>72</v>
+      </c>
+      <c r="H67" t="n">
+        <v>305</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>CLS1003</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>旅游2401 旅游2402 工商实验2401</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>120000251.048</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>形势与政策-3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>工商管理学院</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>新德新</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>xkp01120069</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" t="n">
+        <v>72</v>
+      </c>
+      <c r="H68" t="n">
+        <v>305</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>CLS1003</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>旅游2401 旅游2402 工商实验2401</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>第11-11节</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>120000310.012</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>毛泽东思想和中国特色社会主义理论体系概论</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>工商管理学院</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>新新新</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>xkp01010187</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>4</v>
+      </c>
+      <c r="G69" t="n">
+        <v>107</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>工商2301 工商2302 工商2303 工商2304</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>120000310.012</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>毛泽东思想和中国特色社会主义理论体系概论</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>工商管理学院</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>新新新</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>xkp01010187</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" t="n">
+        <v>107</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>工商2301 工商2302 工商2303 工商2304</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>12100001.043</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>思想道德与法治</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>应急管理学院</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>新斐斐</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>xkp01010168</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>4</v>
+      </c>
+      <c r="G71" t="n">
+        <v>36</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2106</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>CLS1008</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>应急2501</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>12100001.043</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>思想道德与法治</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>应急管理学院</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>新斐斐</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>xkp01010168</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>4</v>
+      </c>
+      <c r="G72" t="n">
+        <v>36</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2106</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>CLS1008</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>应急2501</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>09200007.031</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>C语言程序设计b</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>电气工程与自动化学院</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>新黎娜</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>xkp01070075</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>4</v>
+      </c>
+      <c r="G73" t="n">
+        <v>60</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>信控2503 信控2504</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>09200007.031</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>C语言程序设计b</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>电气工程与自动化学院</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>新黎娜</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>xkp01070075</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>4</v>
+      </c>
+      <c r="G74" t="n">
+        <v>60</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>信控2503 信控2504</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
         <is>
           <t>第3-4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>12100008.069</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>形势与政策-1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>安全科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>新奕雯</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>xkp01230650</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>94</v>
+      </c>
+      <c r="H75" t="n">
+        <v>301</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>CLS1005</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>安全卓2501 安全卓2502 安全卓2503</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>第11-11节</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>12100008.069</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>形势与政策-1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>安全科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>新奕雯</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>xkp01230650</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" t="n">
+        <v>94</v>
+      </c>
+      <c r="H76" t="n">
+        <v>301</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>CLS1005</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>安全卓2501 安全卓2502 安全卓2503</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>04404003.001</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>智能制造工程专业导论</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>新俊杰</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>xkp01080057</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" t="n">
+        <v>120</v>
+      </c>
+      <c r="H77" t="n">
+        <v>305</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>CLS1003</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>04404003.001</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>智能制造工程专业导论</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>新绍亮</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>xkp01080152</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>4</v>
+      </c>
+      <c r="G78" t="n">
+        <v>120</v>
+      </c>
+      <c r="H78" t="n">
+        <v>305</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>CLS1003</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>04404003.001</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>智能制造工程专业导论</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>新俊杰</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>xkp01080057</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>4</v>
+      </c>
+      <c r="G79" t="n">
+        <v>120</v>
+      </c>
+      <c r="H79" t="n">
+        <v>305</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>CLS1003</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>04404003.001</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>智能制造工程专业导论</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>新绍亮</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>xkp01080152</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>4</v>
+      </c>
+      <c r="G80" t="n">
+        <v>120</v>
+      </c>
+      <c r="H80" t="n">
+        <v>305</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>CLS1003</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>智能制造2501 智能制造2502 智能制造2503 智能制造2504</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>120000330.004</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>马克思主义基本原理</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>测绘与国土信息工程学院</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>新新新</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>xkp01230669</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>134</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>遥感2401 遥感2402 遥感2403 遥感2404</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>120000330.004</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>马克思主义基本原理</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>测绘与国土信息工程学院</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>新新新</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>xkp01230669</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>134</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>遥感2401 遥感2402 遥感2403 遥感2404</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>070000030.001</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>材料力学a</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>新亚娟</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>xkp01090069</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" t="n">
+        <v>66</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2106</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>CLS1008</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>机制2401 机制2402</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>070000030.001</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>材料力学a</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>机械与动力工程学院</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>新亚娟</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>xkp01090069</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" t="n">
+        <v>66</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2106</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>CLS1008</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>机制2401 机制2402</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>130123010.001</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>数字图像处理</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>物理与电子信息学院</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>新恺</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>xkp01230576</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>4</v>
+      </c>
+      <c r="G85" t="n">
+        <v>109</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2106</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>CLS1008</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>电信合2301 电信合2302 电信合2303 电信合2304</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>130123010.001</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>数字图像处理</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>物理与电子信息学院</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>新恺</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>xkp01230576</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>4</v>
+      </c>
+      <c r="G86" t="n">
+        <v>109</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2106</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>CLS1008</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>电信合2301 电信合2302 电信合2303 电信合2304</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>251000091.001</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>运筹学</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>土木工程学院</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>新现军</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>xkp01090033</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>4</v>
+      </c>
+      <c r="G87" t="n">
+        <v>52</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2103</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>CLS1006</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>智能建造2401 智能建造2402</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>8,9,10,11,12,13,14,15</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>251000091.001</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>运筹学</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>土木工程学院</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>新现军</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>xkp01090033</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>4</v>
+      </c>
+      <c r="G88" t="n">
+        <v>52</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2103</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>CLS1006</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>智能建造2401 智能建造2402</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>8,9,10,11,12,13,14,15</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>09200005.006</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Python语言程序设计b</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>新本仓</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>xkp01200138</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>4</v>
+      </c>
+      <c r="G89" t="n">
+        <v>63</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>材科2501 材科2502</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>09200005.006</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Python语言程序设计b</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>新本仓</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>xkp01200138</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" t="n">
+        <v>63</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>材科2501 材科2502</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>031011180.001</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>第四纪地质与地貌学</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>资源环境学院</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>新庆</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>xkp01230645</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>4</v>
+      </c>
+      <c r="G91" t="n">
+        <v>57</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2106</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>CLS1008</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>地质2401 地质2402</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>031011180.001</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>第四纪地质与地貌学</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>资源环境学院</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>新庆</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>xkp01230645</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>4</v>
+      </c>
+      <c r="G92" t="n">
+        <v>57</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2106</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>CLS1008</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>地质2401 地质2402</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>050031081.001</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>全球环境变化</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>测绘与国土信息工程学院</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>新新元</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>xkp01110063</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>36</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2106</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>CLS1008</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>自环2301</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>050031081.001</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>全球环境变化</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>测绘与国土信息工程学院</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>新新元</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>xkp01110063</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>36</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2106</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>CLS1008</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>自环2301</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>070030240.002</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>基坑工程</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>土木工程学院</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>新志超</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>xkp01230410</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>4</v>
+      </c>
+      <c r="G95" t="n">
+        <v>28</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2203</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>岩土2301</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>第5-6节</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>070030240.002</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>基坑工程</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>土木工程学院</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>新志超</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>xkp01230410</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>4</v>
+      </c>
+      <c r="G96" t="n">
+        <v>28</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2203</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>岩土2301</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>15ALT021.001</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>乒乓球乙组队</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>新孝志</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>xkp01050019</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>6</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2203</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>第7-8节</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>15ALT021.001</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>乒乓球乙组队</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>新孝志</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>xkp01050019</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>6</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2203</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>15ALT021.001</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>乒乓球乙组队</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>新孝志</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>xkp01050019</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>6</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2203</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20710009.002</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>分析化学</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>新佳佳</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>xkp01230758</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>8</v>
+      </c>
+      <c r="G100" t="n">
+        <v>61</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2203</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>材科2503 材科2504</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>20710009.002</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>分析化学</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>新佳佳</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>xkp01230758</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>8</v>
+      </c>
+      <c r="G101" t="n">
+        <v>61</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2203</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>材科2503 材科2504</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>20710009.002</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>分析化学</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>新佳佳</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>xkp01230758</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>8</v>
+      </c>
+      <c r="G102" t="n">
+        <v>61</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2203</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>材科2503 材科2504</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>周四</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>20710009.002</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>分析化学</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>新佳佳</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>xkp01230758</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>8</v>
+      </c>
+      <c r="G103" t="n">
+        <v>61</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2203</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>材科2503 材科2504</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>2,3,4,5</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>周五</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>15ALT011.001</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>轮滑冰球队</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>新颜东</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>xkp01050061</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>6</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2205</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>CLS1010</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>15ALT011.001</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>轮滑冰球队</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>新颜东</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>xkp01050061</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>6</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2205</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>CLS1010</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>第9-10节</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>15ALT011.001</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>轮滑冰球队</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>新颜东</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>xkp01050061</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>6</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>2205</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>CLS1010</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>周三</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
